--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306786</v>
+        <v>125306784</v>
       </c>
       <c r="B2" t="n">
-        <v>105029</v>
+        <v>108903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422708</v>
+        <v>422715</v>
       </c>
       <c r="R2" t="n">
-        <v>6436105</v>
+        <v>6436086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306784</v>
+        <v>125306786</v>
       </c>
       <c r="B3" t="n">
-        <v>108903</v>
+        <v>105029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422715</v>
+        <v>422708</v>
       </c>
       <c r="R3" t="n">
-        <v>6436086</v>
+        <v>6436105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306784</v>
+        <v>125306786</v>
       </c>
       <c r="B2" t="n">
-        <v>108903</v>
+        <v>105029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422715</v>
+        <v>422708</v>
       </c>
       <c r="R2" t="n">
-        <v>6436086</v>
+        <v>6436105</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306786</v>
+        <v>125306784</v>
       </c>
       <c r="B3" t="n">
-        <v>105029</v>
+        <v>108903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422708</v>
+        <v>422715</v>
       </c>
       <c r="R3" t="n">
-        <v>6436105</v>
+        <v>6436086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306786</v>
+        <v>125306782</v>
       </c>
       <c r="B2" t="n">
-        <v>105029</v>
+        <v>96390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422708</v>
+        <v>422657</v>
       </c>
       <c r="R2" t="n">
-        <v>6436105</v>
+        <v>6436176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306784</v>
+        <v>125306786</v>
       </c>
       <c r="B3" t="n">
-        <v>108903</v>
+        <v>105029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422715</v>
+        <v>422708</v>
       </c>
       <c r="R3" t="n">
-        <v>6436086</v>
+        <v>6436105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125306782</v>
+        <v>125306784</v>
       </c>
       <c r="B4" t="n">
-        <v>96390</v>
+        <v>108903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422657</v>
+        <v>422715</v>
       </c>
       <c r="R4" t="n">
-        <v>6436176</v>
+        <v>6436086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306782</v>
+        <v>125306786</v>
       </c>
       <c r="B2" t="n">
-        <v>96390</v>
+        <v>105205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422657</v>
+        <v>422708</v>
       </c>
       <c r="R2" t="n">
-        <v>6436176</v>
+        <v>6436105</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306786</v>
+        <v>125306782</v>
       </c>
       <c r="B3" t="n">
-        <v>105029</v>
+        <v>96558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422708</v>
+        <v>422657</v>
       </c>
       <c r="R3" t="n">
-        <v>6436105</v>
+        <v>6436176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>125306784</v>
       </c>
       <c r="B4" t="n">
-        <v>108903</v>
+        <v>109082</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306786</v>
+        <v>125306784</v>
       </c>
       <c r="B2" t="n">
-        <v>105205</v>
+        <v>109082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422708</v>
+        <v>422715</v>
       </c>
       <c r="R2" t="n">
-        <v>6436105</v>
+        <v>6436086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125306784</v>
+        <v>125306786</v>
       </c>
       <c r="B4" t="n">
-        <v>109082</v>
+        <v>105205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422715</v>
+        <v>422708</v>
       </c>
       <c r="R4" t="n">
-        <v>6436086</v>
+        <v>6436105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125306784</v>
+        <v>125306782</v>
       </c>
       <c r="B2" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422715</v>
+        <v>422657</v>
       </c>
       <c r="R2" t="n">
-        <v>6436086</v>
+        <v>6436176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306782</v>
+        <v>125306786</v>
       </c>
       <c r="B3" t="n">
-        <v>96558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422657</v>
+        <v>422708</v>
       </c>
       <c r="R3" t="n">
-        <v>6436176</v>
+        <v>6436105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125306786</v>
+        <v>125306784</v>
       </c>
       <c r="B4" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422708</v>
+        <v>422715</v>
       </c>
       <c r="R4" t="n">
-        <v>6436105</v>
+        <v>6436086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125306782</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125306786</v>
       </c>
       <c r="B3" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125306784</v>
       </c>
       <c r="B4" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125306782</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125306786</v>
       </c>
       <c r="B3" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125306784</v>
       </c>
       <c r="B4" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22630-2025 artfynd.xlsx
+++ b/artfynd/A 22630-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125306782</v>
       </c>
       <c r="B2" t="n">
-        <v>96623</v>
+        <v>97394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,27 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125306786</v>
+        <v>125306784</v>
       </c>
       <c r="B3" t="n">
-        <v>105270</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422708</v>
+        <v>422715</v>
       </c>
       <c r="R3" t="n">
-        <v>6436105</v>
+        <v>6436086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,27 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125306784</v>
+        <v>125306786</v>
       </c>
       <c r="B4" t="n">
-        <v>109147</v>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422715</v>
+        <v>422708</v>
       </c>
       <c r="R4" t="n">
-        <v>6436086</v>
+        <v>6436105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
